--- a/artfynd/A 50109-2025 artfynd.xlsx
+++ b/artfynd/A 50109-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,7 +783,7 @@
         <v>129525660</v>
       </c>
       <c r="B3" t="n">
-        <v>95950</v>
+        <v>95953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129525658</v>
       </c>
       <c r="B4" t="n">
-        <v>95950</v>
+        <v>95953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>129525657</v>
       </c>
       <c r="B5" t="n">
-        <v>95950</v>
+        <v>95953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>129525639</v>
       </c>
       <c r="B6" t="n">
-        <v>95960</v>
+        <v>95963</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>129525640</v>
       </c>
       <c r="B7" t="n">
-        <v>95960</v>
+        <v>95963</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>129525659</v>
       </c>
       <c r="B8" t="n">
-        <v>95950</v>
+        <v>95953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>129525638</v>
       </c>
       <c r="B9" t="n">
-        <v>95960</v>
+        <v>95963</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>129525654</v>
       </c>
       <c r="B10" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>129525641</v>
       </c>
       <c r="B11" t="n">
-        <v>95960</v>
+        <v>95963</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,6 +1650,108 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129525649</v>
+      </c>
+      <c r="B12" t="n">
+        <v>102974</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Karlsaflogarna, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>387077</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6401563</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Toarp</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50109-2025 artfynd.xlsx
+++ b/artfynd/A 50109-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129525652</v>
       </c>
       <c r="B2" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>129525660</v>
       </c>
       <c r="B3" t="n">
-        <v>95953</v>
+        <v>95982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129525658</v>
       </c>
       <c r="B4" t="n">
-        <v>95953</v>
+        <v>95982</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>129525657</v>
       </c>
       <c r="B5" t="n">
-        <v>95953</v>
+        <v>95982</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>129525639</v>
       </c>
       <c r="B6" t="n">
-        <v>95963</v>
+        <v>95992</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>129525640</v>
       </c>
       <c r="B7" t="n">
-        <v>95963</v>
+        <v>95992</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>129525659</v>
       </c>
       <c r="B8" t="n">
-        <v>95953</v>
+        <v>95982</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>129525638</v>
       </c>
       <c r="B9" t="n">
-        <v>95963</v>
+        <v>95992</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>129525654</v>
       </c>
       <c r="B10" t="n">
-        <v>97598</v>
+        <v>97627</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>129525641</v>
       </c>
       <c r="B11" t="n">
-        <v>95963</v>
+        <v>95992</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>129525649</v>
       </c>
       <c r="B12" t="n">
-        <v>102974</v>
+        <v>103003</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 50109-2025 artfynd.xlsx
+++ b/artfynd/A 50109-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129525652</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>129525660</v>
       </c>
       <c r="B3" t="n">
-        <v>95982</v>
+        <v>95994</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129525658</v>
       </c>
       <c r="B4" t="n">
-        <v>95982</v>
+        <v>95994</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>129525657</v>
       </c>
       <c r="B5" t="n">
-        <v>95982</v>
+        <v>95994</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>129525639</v>
       </c>
       <c r="B6" t="n">
-        <v>95992</v>
+        <v>96004</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>129525640</v>
       </c>
       <c r="B7" t="n">
-        <v>95992</v>
+        <v>96004</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>129525659</v>
       </c>
       <c r="B8" t="n">
-        <v>95982</v>
+        <v>95994</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>129525638</v>
       </c>
       <c r="B9" t="n">
-        <v>95992</v>
+        <v>96004</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>129525654</v>
       </c>
       <c r="B10" t="n">
-        <v>97627</v>
+        <v>97639</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>129525641</v>
       </c>
       <c r="B11" t="n">
-        <v>95992</v>
+        <v>96004</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>129525649</v>
       </c>
       <c r="B12" t="n">
-        <v>103003</v>
+        <v>103015</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 50109-2025 artfynd.xlsx
+++ b/artfynd/A 50109-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129525652</v>
       </c>
       <c r="B2" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>129525660</v>
       </c>
       <c r="B3" t="n">
-        <v>95994</v>
+        <v>95995</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129525658</v>
       </c>
       <c r="B4" t="n">
-        <v>95994</v>
+        <v>95995</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>129525657</v>
       </c>
       <c r="B5" t="n">
-        <v>95994</v>
+        <v>95995</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>129525639</v>
       </c>
       <c r="B6" t="n">
-        <v>96004</v>
+        <v>96005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>129525640</v>
       </c>
       <c r="B7" t="n">
-        <v>96004</v>
+        <v>96005</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>129525659</v>
       </c>
       <c r="B8" t="n">
-        <v>95994</v>
+        <v>95995</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>129525638</v>
       </c>
       <c r="B9" t="n">
-        <v>96004</v>
+        <v>96005</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>129525654</v>
       </c>
       <c r="B10" t="n">
-        <v>97639</v>
+        <v>97640</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>129525641</v>
       </c>
       <c r="B11" t="n">
-        <v>96004</v>
+        <v>96005</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>129525649</v>
       </c>
       <c r="B12" t="n">
-        <v>103015</v>
+        <v>103016</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 50109-2025 artfynd.xlsx
+++ b/artfynd/A 50109-2025 artfynd.xlsx
@@ -783,7 +783,7 @@
         <v>129525660</v>
       </c>
       <c r="B3" t="n">
-        <v>95995</v>
+        <v>96000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129525658</v>
       </c>
       <c r="B4" t="n">
-        <v>95995</v>
+        <v>96000</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>129525657</v>
       </c>
       <c r="B5" t="n">
-        <v>95995</v>
+        <v>96000</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>129525639</v>
       </c>
       <c r="B6" t="n">
-        <v>96005</v>
+        <v>96010</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>129525640</v>
       </c>
       <c r="B7" t="n">
-        <v>96005</v>
+        <v>96010</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>129525659</v>
       </c>
       <c r="B8" t="n">
-        <v>95995</v>
+        <v>96000</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>129525638</v>
       </c>
       <c r="B9" t="n">
-        <v>96005</v>
+        <v>96010</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>129525654</v>
       </c>
       <c r="B10" t="n">
-        <v>97640</v>
+        <v>97645</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>129525641</v>
       </c>
       <c r="B11" t="n">
-        <v>96005</v>
+        <v>96010</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>129525649</v>
       </c>
       <c r="B12" t="n">
-        <v>103016</v>
+        <v>103021</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 50109-2025 artfynd.xlsx
+++ b/artfynd/A 50109-2025 artfynd.xlsx
@@ -783,7 +783,7 @@
         <v>129525660</v>
       </c>
       <c r="B3" t="n">
-        <v>96000</v>
+        <v>96004</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129525658</v>
       </c>
       <c r="B4" t="n">
-        <v>96000</v>
+        <v>96004</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>129525657</v>
       </c>
       <c r="B5" t="n">
-        <v>96000</v>
+        <v>96004</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>129525639</v>
       </c>
       <c r="B6" t="n">
-        <v>96010</v>
+        <v>96014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>129525640</v>
       </c>
       <c r="B7" t="n">
-        <v>96010</v>
+        <v>96014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>129525659</v>
       </c>
       <c r="B8" t="n">
-        <v>96000</v>
+        <v>96004</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>129525638</v>
       </c>
       <c r="B9" t="n">
-        <v>96010</v>
+        <v>96014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>129525654</v>
       </c>
       <c r="B10" t="n">
-        <v>97645</v>
+        <v>97649</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>129525641</v>
       </c>
       <c r="B11" t="n">
-        <v>96010</v>
+        <v>96014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>129525649</v>
       </c>
       <c r="B12" t="n">
-        <v>103021</v>
+        <v>103025</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 50109-2025 artfynd.xlsx
+++ b/artfynd/A 50109-2025 artfynd.xlsx
@@ -783,7 +783,7 @@
         <v>129525660</v>
       </c>
       <c r="B3" t="n">
-        <v>96004</v>
+        <v>96006</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129525658</v>
       </c>
       <c r="B4" t="n">
-        <v>96004</v>
+        <v>96006</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>129525657</v>
       </c>
       <c r="B5" t="n">
-        <v>96004</v>
+        <v>96006</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>129525639</v>
       </c>
       <c r="B6" t="n">
-        <v>96014</v>
+        <v>96016</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>129525640</v>
       </c>
       <c r="B7" t="n">
-        <v>96014</v>
+        <v>96016</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>129525659</v>
       </c>
       <c r="B8" t="n">
-        <v>96004</v>
+        <v>96006</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>129525638</v>
       </c>
       <c r="B9" t="n">
-        <v>96014</v>
+        <v>96016</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>129525654</v>
       </c>
       <c r="B10" t="n">
-        <v>97649</v>
+        <v>97651</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>129525641</v>
       </c>
       <c r="B11" t="n">
-        <v>96014</v>
+        <v>96016</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>129525649</v>
       </c>
       <c r="B12" t="n">
-        <v>103025</v>
+        <v>103027</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 50109-2025 artfynd.xlsx
+++ b/artfynd/A 50109-2025 artfynd.xlsx
@@ -783,7 +783,7 @@
         <v>129525660</v>
       </c>
       <c r="B3" t="n">
-        <v>96006</v>
+        <v>96016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129525658</v>
       </c>
       <c r="B4" t="n">
-        <v>96006</v>
+        <v>96016</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129525657</v>
+        <v>129525639</v>
       </c>
       <c r="B5" t="n">
-        <v>96006</v>
+        <v>96026</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2809</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>386998</v>
+        <v>387035</v>
       </c>
       <c r="R5" t="n">
-        <v>6401550</v>
+        <v>6401548</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1071,7 +1071,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129525639</v>
+        <v>129525657</v>
       </c>
       <c r="B6" t="n">
         <v>96016</v>
@@ -1082,21 +1082,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2810</v>
+        <v>2809</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>387035</v>
+        <v>386998</v>
       </c>
       <c r="R6" t="n">
-        <v>6401548</v>
+        <v>6401550</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1171,7 +1171,7 @@
         <v>129525640</v>
       </c>
       <c r="B7" t="n">
-        <v>96016</v>
+        <v>96026</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>129525659</v>
       </c>
       <c r="B8" t="n">
-        <v>96006</v>
+        <v>96016</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>129525638</v>
       </c>
       <c r="B9" t="n">
-        <v>96016</v>
+        <v>96026</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>129525654</v>
       </c>
       <c r="B10" t="n">
-        <v>97651</v>
+        <v>97661</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>129525641</v>
       </c>
       <c r="B11" t="n">
-        <v>96016</v>
+        <v>96026</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>129525649</v>
       </c>
       <c r="B12" t="n">
-        <v>103027</v>
+        <v>103037</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 50109-2025 artfynd.xlsx
+++ b/artfynd/A 50109-2025 artfynd.xlsx
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129525639</v>
+        <v>129525657</v>
       </c>
       <c r="B5" t="n">
-        <v>96026</v>
+        <v>96016</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>2809</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>387035</v>
+        <v>386998</v>
       </c>
       <c r="R5" t="n">
-        <v>6401548</v>
+        <v>6401550</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129525657</v>
+        <v>129525639</v>
       </c>
       <c r="B6" t="n">
-        <v>96016</v>
+        <v>96026</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,21 +1082,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2809</v>
+        <v>2810</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>386998</v>
+        <v>387035</v>
       </c>
       <c r="R6" t="n">
-        <v>6401550</v>
+        <v>6401548</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>

--- a/artfynd/A 50109-2025 artfynd.xlsx
+++ b/artfynd/A 50109-2025 artfynd.xlsx
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129525657</v>
+        <v>129525639</v>
       </c>
       <c r="B5" t="n">
-        <v>96016</v>
+        <v>96026</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2809</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>386998</v>
+        <v>387035</v>
       </c>
       <c r="R5" t="n">
-        <v>6401550</v>
+        <v>6401548</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129525639</v>
+        <v>129525657</v>
       </c>
       <c r="B6" t="n">
-        <v>96026</v>
+        <v>96016</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,21 +1082,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2810</v>
+        <v>2809</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>387035</v>
+        <v>386998</v>
       </c>
       <c r="R6" t="n">
-        <v>6401548</v>
+        <v>6401550</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>

--- a/artfynd/A 50109-2025 artfynd.xlsx
+++ b/artfynd/A 50109-2025 artfynd.xlsx
@@ -1656,7 +1656,7 @@
         <v>129525649</v>
       </c>
       <c r="B12" t="n">
-        <v>103037</v>
+        <v>103041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 50109-2025 artfynd.xlsx
+++ b/artfynd/A 50109-2025 artfynd.xlsx
@@ -1656,7 +1656,7 @@
         <v>129525649</v>
       </c>
       <c r="B12" t="n">
-        <v>103041</v>
+        <v>103044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 50109-2025 artfynd.xlsx
+++ b/artfynd/A 50109-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129525652</v>
+        <v>129525657</v>
       </c>
       <c r="B2" t="n">
-        <v>57733</v>
+        <v>96338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Karlsaflogarna, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>387008</v>
+        <v>386998</v>
       </c>
       <c r="R2" t="n">
-        <v>6401566</v>
+        <v>6401550</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -780,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129525660</v>
+        <v>129525658</v>
       </c>
       <c r="B3" t="n">
-        <v>96016</v>
+        <v>96338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>387029</v>
+        <v>386993</v>
       </c>
       <c r="R3" t="n">
-        <v>6401552</v>
+        <v>6401533</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -877,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129525658</v>
+        <v>129525659</v>
       </c>
       <c r="B4" t="n">
-        <v>96016</v>
+        <v>96338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>386993</v>
+        <v>387007</v>
       </c>
       <c r="R4" t="n">
-        <v>6401533</v>
+        <v>6401566</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -974,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129525639</v>
+        <v>129525660</v>
       </c>
       <c r="B5" t="n">
-        <v>96026</v>
+        <v>96338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>2809</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>387035</v>
+        <v>387029</v>
       </c>
       <c r="R5" t="n">
-        <v>6401548</v>
+        <v>6401552</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1071,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129525657</v>
+        <v>129525638</v>
       </c>
       <c r="B6" t="n">
-        <v>96016</v>
+        <v>96348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2809</v>
+        <v>2810</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>386998</v>
+        <v>386993</v>
       </c>
       <c r="R6" t="n">
-        <v>6401550</v>
+        <v>6401548</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1168,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129525640</v>
+        <v>129525639</v>
       </c>
       <c r="B7" t="n">
-        <v>96026</v>
+        <v>96348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>387046</v>
+        <v>387035</v>
       </c>
       <c r="R7" t="n">
-        <v>6401544</v>
+        <v>6401548</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1265,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129525659</v>
+        <v>129525640</v>
       </c>
       <c r="B8" t="n">
-        <v>96016</v>
+        <v>96348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1276,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2809</v>
+        <v>2810</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1300,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>387007</v>
+        <v>387046</v>
       </c>
       <c r="R8" t="n">
-        <v>6401566</v>
+        <v>6401544</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1362,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129525638</v>
+        <v>129525641</v>
       </c>
       <c r="B9" t="n">
-        <v>96026</v>
+        <v>96348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1397,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>386993</v>
+        <v>387078</v>
       </c>
       <c r="R9" t="n">
-        <v>6401548</v>
+        <v>6401582</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1459,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129525654</v>
+        <v>129525652</v>
       </c>
       <c r="B10" t="n">
-        <v>97661</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1470,34 +1462,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Karlsaflogarna, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>387038</v>
+        <v>387008</v>
       </c>
       <c r="R10" t="n">
-        <v>6401555</v>
+        <v>6401566</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1556,32 +1556,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129525641</v>
+        <v>129525672</v>
       </c>
       <c r="B11" t="n">
-        <v>96026</v>
+        <v>106812</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2810</v>
+        <v>220785</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>387078</v>
+        <v>387100</v>
       </c>
       <c r="R11" t="n">
-        <v>6401582</v>
+        <v>6401564</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1653,49 +1653,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129525649</v>
+        <v>129525654</v>
       </c>
       <c r="B12" t="n">
-        <v>103044</v>
+        <v>97983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223246</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Karlsaflogarna, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>387077</v>
+        <v>387038</v>
       </c>
       <c r="R12" t="n">
-        <v>6401563</v>
+        <v>6401555</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1736,7 +1732,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1752,6 +1747,108 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129525649</v>
+      </c>
+      <c r="B13" t="n">
+        <v>103402</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Karlsaflogarna, Vg</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>387077</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6401563</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Toarp</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50109-2025 artfynd.xlsx
+++ b/artfynd/A 50109-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129525657</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129525658</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129525659</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129525660</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129525638</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129525639</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129525640</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129525641</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1553,6 +1598,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129525652</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1650,6 +1700,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129525672</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1747,6 +1802,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129525654</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1849,8 +1909,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129525649</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>